--- a/Team-Data/2008-09/4-14-2008-09.xlsx
+++ b/Team-Data/2008-09/4-14-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
         <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>0.58</v>
+        <v>0.575</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
@@ -688,7 +755,7 @@
         <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N2" t="n">
         <v>0.366</v>
@@ -700,16 +767,16 @@
         <v>25.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S2" t="n">
         <v>29.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
         <v>20.3</v>
@@ -727,25 +794,25 @@
         <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA2" t="n">
         <v>20.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,10 +821,10 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>24</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>10</v>
@@ -766,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN2" t="n">
         <v>16</v>
@@ -796,7 +863,7 @@
         <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>20</v>
@@ -811,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -858,31 +925,31 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.397</v>
+        <v>0.393</v>
       </c>
       <c r="O3" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P3" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -894,7 +961,7 @@
         <v>42.2</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.6</v>
@@ -903,7 +970,7 @@
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -912,16 +979,16 @@
         <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -936,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="AI3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -957,16 +1024,16 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
         <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -981,22 +1048,22 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-1</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1178,7 +1245,7 @@
         <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -1207,31 +1274,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.457</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
@@ -1240,13 +1307,13 @@
         <v>0.383</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.8</v>
@@ -1276,16 +1343,16 @@
         <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
         <v>102.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>15</v>
@@ -1297,7 +1364,7 @@
         <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1318,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1336,13 +1403,13 @@
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1351,7 +1418,7 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
         <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.825</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.468</v>
@@ -1416,16 +1483,16 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0.758</v>
@@ -1440,34 +1507,34 @@
         <v>42.3</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z6" t="n">
         <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1485,13 +1552,13 @@
         <v>15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
@@ -1500,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1512,28 +1579,28 @@
         <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
         <v>6</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1676,7 +1743,7 @@
         <v>12</v>
       </c>
       <c r="AM7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN7" t="n">
         <v>27</v>
@@ -1694,7 +1761,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,10 +1910,10 @@
         <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -2076,10 +2143,10 @@
         <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2249,7 +2316,7 @@
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -2377,22 +2444,22 @@
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ11" t="n">
         <v>21</v>
@@ -2410,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
@@ -2419,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
@@ -2571,7 +2638,7 @@
         <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2595,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
@@ -2792,7 +2859,7 @@
         <v>24</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>23</v>
@@ -2807,7 +2874,7 @@
         <v>19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -2860,13 +2927,13 @@
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
         <v>6.7</v>
@@ -2878,7 +2945,7 @@
         <v>0.359</v>
       </c>
       <c r="O14" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P14" t="n">
         <v>25.5</v>
@@ -2890,19 +2957,19 @@
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.4</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
         <v>13.4</v>
       </c>
       <c r="W14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>5.1</v>
@@ -2911,19 +2978,19 @@
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.1</v>
+        <v>106.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2968,37 +3035,37 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3141,7 +3208,7 @@
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
         <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.519</v>
+        <v>0.525</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J16" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O16" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P16" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R16" t="n">
         <v>10</v>
@@ -3257,13 +3324,13 @@
         <v>29.3</v>
       </c>
       <c r="T16" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U16" t="n">
         <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="W16" t="n">
         <v>8</v>
@@ -3281,13 +3348,13 @@
         <v>19.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC16" t="n">
         <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3299,31 +3366,31 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
         <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>23</v>
@@ -3353,13 +3420,13 @@
         <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" t="n">
         <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I17" t="n">
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>6.2</v>
       </c>
       <c r="M17" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
         <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0.78</v>
@@ -3436,10 +3503,10 @@
         <v>11.8</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U17" t="n">
         <v>21.9</v>
@@ -3457,7 +3524,7 @@
         <v>4.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
         <v>22.6</v>
@@ -3466,16 +3533,16 @@
         <v>99.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
@@ -3502,10 +3569,10 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3544,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3857,7 +3924,7 @@
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
@@ -3893,7 +3960,7 @@
         <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
@@ -3905,7 +3972,7 @@
         <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>13</v>
@@ -4069,7 +4136,7 @@
         <v>28</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4412,7 +4479,7 @@
         <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4621,7 +4688,7 @@
         <v>21</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,7 +4750,7 @@
         <v>36.5</v>
       </c>
       <c r="J24" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K24" t="n">
         <v>0.458</v>
@@ -4695,25 +4762,25 @@
         <v>13.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="O24" t="n">
         <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R24" t="n">
         <v>12.7</v>
       </c>
       <c r="S24" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
         <v>20.1</v>
@@ -4725,7 +4792,7 @@
         <v>8</v>
       </c>
       <c r="X24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
         <v>4.9</v>
@@ -4743,13 +4810,13 @@
         <v>0.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF24" t="n">
         <v>15</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>16</v>
       </c>
       <c r="AG24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4976,7 +5043,7 @@
         <v>14</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4991,7 +5058,7 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
         <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.663</v>
+        <v>0.654</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5062,22 +5129,22 @@
         <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U26" t="n">
         <v>20.2</v>
@@ -5098,22 +5165,22 @@
         <v>20.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
         <v>6</v>
@@ -5128,7 +5195,7 @@
         <v>23</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>9</v>
@@ -5137,16 +5204,16 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,13 +5225,13 @@
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -5471,34 +5538,34 @@
         <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
       </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="n">
         <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
         <v>20</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>6</v>
       </c>
       <c r="AM28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5680,13 +5747,13 @@
         <v>24</v>
       </c>
       <c r="AM29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN29" t="n">
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
         <v>25</v>
@@ -5713,10 +5780,10 @@
         <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E30" t="n">
         <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.585</v>
+        <v>0.593</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5778,7 +5845,7 @@
         <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5787,40 +5854,40 @@
         <v>13.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O30" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="P30" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U30" t="n">
         <v>24.7</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z30" t="n">
         <v>22.3</v>
@@ -5829,10 +5896,10 @@
         <v>24</v>
       </c>
       <c r="AB30" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5847,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5859,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6029,7 +6096,7 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
@@ -6041,7 +6108,7 @@
         <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM31" t="n">
         <v>25</v>
@@ -6056,7 +6123,7 @@
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6083,10 +6150,10 @@
         <v>22</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-14-2008-09</t>
+          <t>2009-04-14</t>
         </is>
       </c>
     </row>
